--- a/Отчёты/localhost_2026-09-01_image-audit.xlsx
+++ b/Отчёты/localhost_2026-09-01_image-audit.xlsx
@@ -17,7 +17,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">'Risk'!A1:Q16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3">'External Matches'!A1:G2</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">'Metadata'!A1:Q16</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Duplicates'!A1:F11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5">'Duplicates'!A1:P11</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="6">'Large Images'!A1:E5</definedName>
   </definedNames>
 </workbook>
@@ -444,7 +444,7 @@
         <v>Дата запуска</v>
       </c>
       <c r="B5" t="str">
-        <v>01.09.2026, 09:16:34</v>
+        <v>01.09.2026, 13:08:27</v>
       </c>
     </row>
     <row r="7">
@@ -548,7 +548,7 @@
         <v>SHA-256 рассчитан</v>
       </c>
       <c r="B22">
-        <v>20</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -684,7 +684,7 @@
         <v>Время выполнения</v>
       </c>
       <c r="B44" t="str">
-        <v>0 ч. 0 мин. 8 сек.</v>
+        <v>0 ч. 8 мин. 20 сек.</v>
       </c>
     </row>
   </sheetData>
@@ -3542,14 +3542,24 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:P11"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="70.83203125" customWidth="1"/>
-    <col min="5" max="5" width="70.83203125" customWidth="1"/>
-    <col min="6" max="6" width="30.83203125" customWidth="1"/>
+    <col min="5" max="5" width="65.83203125" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" customWidth="1"/>
+    <col min="7" max="7" width="30.83203125" customWidth="1"/>
+    <col min="8" max="8" width="30.83203125" customWidth="1"/>
+    <col min="9" max="9" width="65.83203125" customWidth="1"/>
+    <col min="10" max="10" width="25.83203125" customWidth="1"/>
+    <col min="11" max="11" width="30.83203125" customWidth="1"/>
+    <col min="12" max="12" width="30.83203125" customWidth="1"/>
+    <col min="13" max="13" width="70.83203125" customWidth="1"/>
+    <col min="14" max="14" width="45.83203125" customWidth="1"/>
+    <col min="15" max="15" width="70.83203125" customWidth="1"/>
+    <col min="16" max="16" width="30.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3563,12 +3573,42 @@
         <v>Threshold</v>
       </c>
       <c r="D1" t="str">
+        <v>SHA-256</v>
+      </c>
+      <c r="E1" t="str">
+        <v>Representative</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Metadata Author</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Metadata Copyright</v>
+      </c>
+      <c r="H1" t="str">
+        <v>Metadata Rights</v>
+      </c>
+      <c r="I1" t="str">
+        <v>Web Statement</v>
+      </c>
+      <c r="J1" t="str">
+        <v>Asset ID</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Credit</v>
+      </c>
+      <c r="L1" t="str">
+        <v>By-line</v>
+      </c>
+      <c r="M1" t="str">
         <v>Image URL</v>
       </c>
-      <c r="E1" t="str">
-        <v>SHA-256</v>
-      </c>
-      <c r="F1" t="str">
+      <c r="N1" t="str">
+        <v>Page URL</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Image SHA-256</v>
+      </c>
+      <c r="P1" t="str">
         <v>pHash</v>
       </c>
     </row>
@@ -3583,13 +3623,43 @@
         <v>—</v>
       </c>
       <c r="D2" t="str">
+        <v>6bdfaaa0d913ad6eed4671a001525abebefe1172cb0db5d1bfe9c237eeaeebe1</v>
+      </c>
+      <c r="E2" t="str">
         <v>http://localhost:3000/img/test2.jpg</v>
       </c>
-      <c r="E2" t="str">
+      <c r="F2" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="G2" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="H2" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="I2" t="str">
+        <v>https://www.istockphoto.com/legal/license-agreement?utm_medium=organic&amp;utm_source=google&amp;utm_campaign=iptcurl</v>
+      </c>
+      <c r="J2" t="str">
+        <v>637785818</v>
+      </c>
+      <c r="K2" t="str">
+        <v>Getty Images</v>
+      </c>
+      <c r="L2" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="M2" t="str">
+        <v>http://localhost:3000/img/test2.jpg</v>
+      </c>
+      <c r="N2" t="str">
+        <v>http://localhost:3000/</v>
+      </c>
+      <c r="O2" t="str">
         <v>6bdfaaa0d913ad6eed4671a001525abebefe1172cb0db5d1bfe9c237eeaeebe1</v>
       </c>
-      <c r="F2" t="str">
-        <v>—</v>
+      <c r="P2" t="str">
+        <v>111010011101010110100100111001111001011100010100110001010001000</v>
       </c>
     </row>
     <row r="3">
@@ -3603,13 +3673,43 @@
         <v>—</v>
       </c>
       <c r="D3" t="str">
+        <v>6bdfaaa0d913ad6eed4671a001525abebefe1172cb0db5d1bfe9c237eeaeebe1</v>
+      </c>
+      <c r="E3" t="str">
         <v>http://localhost:3000/img/test2.jpg</v>
       </c>
-      <c r="E3" t="str">
+      <c r="F3" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="G3" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="H3" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="I3" t="str">
+        <v>https://www.istockphoto.com/legal/license-agreement?utm_medium=organic&amp;utm_source=google&amp;utm_campaign=iptcurl</v>
+      </c>
+      <c r="J3" t="str">
+        <v>637785818</v>
+      </c>
+      <c r="K3" t="str">
+        <v>Getty Images</v>
+      </c>
+      <c r="L3" t="str">
+        <v>xubingruo</v>
+      </c>
+      <c r="M3" t="str">
+        <v>http://localhost:3000/img/test2.jpg</v>
+      </c>
+      <c r="N3" t="str">
+        <v>http://localhost:3000/index.html</v>
+      </c>
+      <c r="O3" t="str">
         <v>6bdfaaa0d913ad6eed4671a001525abebefe1172cb0db5d1bfe9c237eeaeebe1</v>
       </c>
-      <c r="F3" t="str">
-        <v>—</v>
+      <c r="P3" t="str">
+        <v>111010011101010110100100111001111001011100010100110001010001000</v>
       </c>
     </row>
     <row r="4">
@@ -3623,13 +3723,43 @@
         <v>—</v>
       </c>
       <c r="D4" t="str">
+        <v>8e9af23b342c1f0952a600d30e988f0499938bce45164c9bb373cac9991a996d</v>
+      </c>
+      <c r="E4" t="str">
         <v>http://localhost:3000/img/image_2.png</v>
       </c>
-      <c r="E4" t="str">
+      <c r="F4" t="str">
+        <v>—</v>
+      </c>
+      <c r="G4" t="str">
+        <v>—</v>
+      </c>
+      <c r="H4" t="str">
+        <v>—</v>
+      </c>
+      <c r="I4" t="str">
+        <v>—</v>
+      </c>
+      <c r="J4" t="str">
+        <v>—</v>
+      </c>
+      <c r="K4" t="str">
+        <v>—</v>
+      </c>
+      <c r="L4" t="str">
+        <v>—</v>
+      </c>
+      <c r="M4" t="str">
+        <v>http://localhost:3000/img/image_2.png</v>
+      </c>
+      <c r="N4" t="str">
+        <v>http://localhost:3000/</v>
+      </c>
+      <c r="O4" t="str">
         <v>8e9af23b342c1f0952a600d30e988f0499938bce45164c9bb373cac9991a996d</v>
       </c>
-      <c r="F4" t="str">
-        <v>—</v>
+      <c r="P4" t="str">
+        <v>111100001100111001110010001101110000100100101001001111010000101</v>
       </c>
     </row>
     <row r="5">
@@ -3643,13 +3773,43 @@
         <v>—</v>
       </c>
       <c r="D5" t="str">
+        <v>8e9af23b342c1f0952a600d30e988f0499938bce45164c9bb373cac9991a996d</v>
+      </c>
+      <c r="E5" t="str">
         <v>http://localhost:3000/img/image_2.png</v>
       </c>
-      <c r="E5" t="str">
+      <c r="F5" t="str">
+        <v>—</v>
+      </c>
+      <c r="G5" t="str">
+        <v>—</v>
+      </c>
+      <c r="H5" t="str">
+        <v>—</v>
+      </c>
+      <c r="I5" t="str">
+        <v>—</v>
+      </c>
+      <c r="J5" t="str">
+        <v>—</v>
+      </c>
+      <c r="K5" t="str">
+        <v>—</v>
+      </c>
+      <c r="L5" t="str">
+        <v>—</v>
+      </c>
+      <c r="M5" t="str">
+        <v>http://localhost:3000/img/image_2.png</v>
+      </c>
+      <c r="N5" t="str">
+        <v>http://localhost:3000/index.html</v>
+      </c>
+      <c r="O5" t="str">
         <v>8e9af23b342c1f0952a600d30e988f0499938bce45164c9bb373cac9991a996d</v>
       </c>
-      <c r="F5" t="str">
-        <v>—</v>
+      <c r="P5" t="str">
+        <v>111100001100111001110010001101110000100100101001001111010000101</v>
       </c>
     </row>
     <row r="6">
@@ -3663,13 +3823,43 @@
         <v>—</v>
       </c>
       <c r="D6" t="str">
+        <v>54a6a35466a655786e62d4c9d002362a55a7ac901700658e14051de39da66961</v>
+      </c>
+      <c r="E6" t="str">
         <v>http://localhost:3000/img/image_3.png</v>
       </c>
-      <c r="E6" t="str">
+      <c r="F6" t="str">
+        <v>—</v>
+      </c>
+      <c r="G6" t="str">
+        <v>—</v>
+      </c>
+      <c r="H6" t="str">
+        <v>—</v>
+      </c>
+      <c r="I6" t="str">
+        <v>—</v>
+      </c>
+      <c r="J6" t="str">
+        <v>—</v>
+      </c>
+      <c r="K6" t="str">
+        <v>—</v>
+      </c>
+      <c r="L6" t="str">
+        <v>—</v>
+      </c>
+      <c r="M6" t="str">
+        <v>http://localhost:3000/img/image_3.png</v>
+      </c>
+      <c r="N6" t="str">
+        <v>http://localhost:3000/</v>
+      </c>
+      <c r="O6" t="str">
         <v>54a6a35466a655786e62d4c9d002362a55a7ac901700658e14051de39da66961</v>
       </c>
-      <c r="F6" t="str">
-        <v>—</v>
+      <c r="P6" t="str">
+        <v>101010111010100001111101101111101101110110101010011111110010101</v>
       </c>
     </row>
     <row r="7">
@@ -3683,13 +3873,43 @@
         <v>—</v>
       </c>
       <c r="D7" t="str">
+        <v>54a6a35466a655786e62d4c9d002362a55a7ac901700658e14051de39da66961</v>
+      </c>
+      <c r="E7" t="str">
         <v>http://localhost:3000/img/image_3.png</v>
       </c>
-      <c r="E7" t="str">
+      <c r="F7" t="str">
+        <v>—</v>
+      </c>
+      <c r="G7" t="str">
+        <v>—</v>
+      </c>
+      <c r="H7" t="str">
+        <v>—</v>
+      </c>
+      <c r="I7" t="str">
+        <v>—</v>
+      </c>
+      <c r="J7" t="str">
+        <v>—</v>
+      </c>
+      <c r="K7" t="str">
+        <v>—</v>
+      </c>
+      <c r="L7" t="str">
+        <v>—</v>
+      </c>
+      <c r="M7" t="str">
+        <v>http://localhost:3000/img/image_3.png</v>
+      </c>
+      <c r="N7" t="str">
+        <v>http://localhost:3000/index.html</v>
+      </c>
+      <c r="O7" t="str">
         <v>54a6a35466a655786e62d4c9d002362a55a7ac901700658e14051de39da66961</v>
       </c>
-      <c r="F7" t="str">
-        <v>—</v>
+      <c r="P7" t="str">
+        <v>101010111010100001111101101111101101110110101010011111110010101</v>
       </c>
     </row>
     <row r="8">
@@ -3703,13 +3923,43 @@
         <v>—</v>
       </c>
       <c r="D8" t="str">
+        <v>7da2815cb84db4d40d097f9866110c47ab71309cdd1732add81a0b1ed58d98c8</v>
+      </c>
+      <c r="E8" t="str">
         <v>http://localhost:3000/img/image_4.png</v>
       </c>
-      <c r="E8" t="str">
+      <c r="F8" t="str">
+        <v>—</v>
+      </c>
+      <c r="G8" t="str">
+        <v>—</v>
+      </c>
+      <c r="H8" t="str">
+        <v>—</v>
+      </c>
+      <c r="I8" t="str">
+        <v>—</v>
+      </c>
+      <c r="J8" t="str">
+        <v>—</v>
+      </c>
+      <c r="K8" t="str">
+        <v>—</v>
+      </c>
+      <c r="L8" t="str">
+        <v>—</v>
+      </c>
+      <c r="M8" t="str">
+        <v>http://localhost:3000/img/image_4.png</v>
+      </c>
+      <c r="N8" t="str">
+        <v>http://localhost:3000/</v>
+      </c>
+      <c r="O8" t="str">
         <v>7da2815cb84db4d40d097f9866110c47ab71309cdd1732add81a0b1ed58d98c8</v>
       </c>
-      <c r="F8" t="str">
-        <v>—</v>
+      <c r="P8" t="str">
+        <v>010111000100010100001001000010010000000001011000010001110001110</v>
       </c>
     </row>
     <row r="9">
@@ -3723,13 +3973,43 @@
         <v>—</v>
       </c>
       <c r="D9" t="str">
+        <v>7da2815cb84db4d40d097f9866110c47ab71309cdd1732add81a0b1ed58d98c8</v>
+      </c>
+      <c r="E9" t="str">
         <v>http://localhost:3000/img/image_4.png</v>
       </c>
-      <c r="E9" t="str">
+      <c r="F9" t="str">
+        <v>—</v>
+      </c>
+      <c r="G9" t="str">
+        <v>—</v>
+      </c>
+      <c r="H9" t="str">
+        <v>—</v>
+      </c>
+      <c r="I9" t="str">
+        <v>—</v>
+      </c>
+      <c r="J9" t="str">
+        <v>—</v>
+      </c>
+      <c r="K9" t="str">
+        <v>—</v>
+      </c>
+      <c r="L9" t="str">
+        <v>—</v>
+      </c>
+      <c r="M9" t="str">
+        <v>http://localhost:3000/img/image_4.png</v>
+      </c>
+      <c r="N9" t="str">
+        <v>http://localhost:3000/index.html</v>
+      </c>
+      <c r="O9" t="str">
         <v>7da2815cb84db4d40d097f9866110c47ab71309cdd1732add81a0b1ed58d98c8</v>
       </c>
-      <c r="F9" t="str">
-        <v>—</v>
+      <c r="P9" t="str">
+        <v>010111000100010100001001000010010000000001011000010001110001110</v>
       </c>
     </row>
     <row r="10">
@@ -3743,13 +4023,43 @@
         <v>—</v>
       </c>
       <c r="D10" t="str">
+        <v>d3f2c190fd7394d50fd98bd7b941b1582d612bfd6547f3bbc533b9f4d35b3d67</v>
+      </c>
+      <c r="E10" t="str">
         <v>http://localhost:3000/img/image_5.jpeg</v>
       </c>
-      <c r="E10" t="str">
+      <c r="F10" t="str">
+        <v>—</v>
+      </c>
+      <c r="G10" t="str">
+        <v>—</v>
+      </c>
+      <c r="H10" t="str">
+        <v>—</v>
+      </c>
+      <c r="I10" t="str">
+        <v>—</v>
+      </c>
+      <c r="J10" t="str">
+        <v>—</v>
+      </c>
+      <c r="K10" t="str">
+        <v>—</v>
+      </c>
+      <c r="L10" t="str">
+        <v>—</v>
+      </c>
+      <c r="M10" t="str">
+        <v>http://localhost:3000/img/image_5.jpeg</v>
+      </c>
+      <c r="N10" t="str">
+        <v>http://localhost:3000/</v>
+      </c>
+      <c r="O10" t="str">
         <v>d3f2c190fd7394d50fd98bd7b941b1582d612bfd6547f3bbc533b9f4d35b3d67</v>
       </c>
-      <c r="F10" t="str">
-        <v>—</v>
+      <c r="P10" t="str">
+        <v>011100100000111110000001100000011000001110010001100001100100000</v>
       </c>
     </row>
     <row r="11">
@@ -3763,19 +4073,49 @@
         <v>—</v>
       </c>
       <c r="D11" t="str">
+        <v>d3f2c190fd7394d50fd98bd7b941b1582d612bfd6547f3bbc533b9f4d35b3d67</v>
+      </c>
+      <c r="E11" t="str">
         <v>http://localhost:3000/img/image_5.jpeg</v>
       </c>
-      <c r="E11" t="str">
+      <c r="F11" t="str">
+        <v>—</v>
+      </c>
+      <c r="G11" t="str">
+        <v>—</v>
+      </c>
+      <c r="H11" t="str">
+        <v>—</v>
+      </c>
+      <c r="I11" t="str">
+        <v>—</v>
+      </c>
+      <c r="J11" t="str">
+        <v>—</v>
+      </c>
+      <c r="K11" t="str">
+        <v>—</v>
+      </c>
+      <c r="L11" t="str">
+        <v>—</v>
+      </c>
+      <c r="M11" t="str">
+        <v>http://localhost:3000/img/image_5.jpeg</v>
+      </c>
+      <c r="N11" t="str">
+        <v>http://localhost:3000/index.html</v>
+      </c>
+      <c r="O11" t="str">
         <v>d3f2c190fd7394d50fd98bd7b941b1582d612bfd6547f3bbc533b9f4d35b3d67</v>
       </c>
-      <c r="F11" t="str">
-        <v>—</v>
+      <c r="P11" t="str">
+        <v>011100100000111110000001100000011000001110010001100001100100000</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:F11"/>
+  <autoFilter ref="A1:P11"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F11"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:P11"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/Отчёты/localhost_2026-09-01_image-audit.xlsx
+++ b/Отчёты/localhost_2026-09-01_image-audit.xlsx
@@ -444,7 +444,7 @@
         <v>Дата запуска</v>
       </c>
       <c r="B5" t="str">
-        <v>01.09.2026, 13:08:27</v>
+        <v>01.09.2026, 14:55:29</v>
       </c>
     </row>
     <row r="7">
@@ -684,7 +684,7 @@
         <v>Время выполнения</v>
       </c>
       <c r="B44" t="str">
-        <v>0 ч. 8 мин. 20 сек.</v>
+        <v>0 ч. 8 мин. 12 сек.</v>
       </c>
     </row>
   </sheetData>
